--- a/information_forms/023_note_creation_and_management_form--information_forms.xlsx
+++ b/information_forms/023_note_creation_and_management_form--information_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -819,8 +819,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -848,12 +848,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'meeting_records',_'label':_'meeting_records'}</t>
+          <t>meeting_records</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Meeting Records', 'label': 'Meeting Records'}</t>
+          <t>Meeting Records</t>
         </is>
       </c>
     </row>
@@ -865,12 +865,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'project_updates',_'label':_'project_updates'}</t>
+          <t>project_updates</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Project Updates', 'label': 'Project Updates'}</t>
+          <t>Project Updates</t>
         </is>
       </c>
     </row>
@@ -882,12 +882,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'follow-ups',_'label':_'follow-ups'}</t>
+          <t>follow-ups</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Follow-ups', 'label': 'Follow-ups'}</t>
+          <t>Follow-ups</t>
         </is>
       </c>
     </row>
@@ -899,12 +899,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'team_members',_'label':_'team_members'}</t>
+          <t>team_members</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Team Members', 'label': 'Team Members'}</t>
+          <t>Team Members</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'manager',_'label':_'manager'}</t>
+          <t>manager</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Manager', 'label': 'Manager'}</t>
+          <t>Manager</t>
         </is>
       </c>
     </row>
@@ -933,12 +933,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'meeting_minutes',_'label':_'meeting_minutes'}</t>
+          <t>meeting_minutes</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Meeting Minutes', 'label': 'Meeting Minutes'}</t>
+          <t>Meeting Minutes</t>
         </is>
       </c>
     </row>
@@ -950,12 +950,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'meeting_notes',_'label':_'meeting_notes'}</t>
+          <t>meeting_notes</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Meeting Notes', 'label': 'Meeting Notes'}</t>
+          <t>Meeting Notes</t>
         </is>
       </c>
     </row>
@@ -967,12 +967,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'project_status',_'label':_'project_status'}</t>
+          <t>project_status</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Project Status', 'label': 'Project Status'}</t>
+          <t>Project Status</t>
         </is>
       </c>
     </row>
@@ -984,12 +984,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'in_progress',_'label':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'In Progress', 'label': 'In Progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -1001,12 +1001,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'complete',_'label':_'complete'}</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Complete', 'label': 'Complete'}</t>
+          <t>Complete</t>
         </is>
       </c>
     </row>
@@ -1018,12 +1018,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'new',_'label':_'new'}</t>
+          <t>new</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'New', 'label': 'New'}</t>
+          <t>New</t>
         </is>
       </c>
     </row>
@@ -1035,12 +1035,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'completed',_'label':_'completed'}</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Completed', 'label': 'Completed'}</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
